--- a/artfynd/A 14025-2024 artfynd.xlsx
+++ b/artfynd/A 14025-2024 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14025-2024 artfynd.xlsx
+++ b/artfynd/A 14025-2024 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14025-2024 artfynd.xlsx
+++ b/artfynd/A 14025-2024 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14025-2024 artfynd.xlsx
+++ b/artfynd/A 14025-2024 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14025-2024 artfynd.xlsx
+++ b/artfynd/A 14025-2024 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14025-2024 artfynd.xlsx
+++ b/artfynd/A 14025-2024 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14025-2024 artfynd.xlsx
+++ b/artfynd/A 14025-2024 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14025-2024 artfynd.xlsx
+++ b/artfynd/A 14025-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,131 +1177,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>121344482</v>
-      </c>
-      <c r="B6" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Långvak, ONO om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>371701</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6616103</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>S-Arv-0606</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4 dellokaler rapporterade. RT90: 6619929-1326276, 29 ex; 6619933-1326265, 11 ex; 6619960-1326323, 46 ex; 6619967-1326247, 12 ex [oklart om det avser antal skott eller blomstänglar]</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Lisa Ingwall-King</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
